--- a/test_sdelka.xlsx
+++ b/test_sdelka.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Yaroslav\python_script\ringo_task\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24A875EF-1982-49A7-8E79-E37AD6FAD968}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{113E3898-01A3-48A9-9E05-7802796EFEFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-7845" yWindow="-15630" windowWidth="37515" windowHeight="13335" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -760,7 +760,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -785,12 +785,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="22" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -883,10 +877,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="D3DAE3"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="404552"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -1141,7 +1135,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U52"/>
+  <dimension ref="A1:U51"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="6" width="8.7265625" style="1"/>
@@ -1801,7 +1795,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="78.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21" ht="65.5" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
         <v>2249</v>
       </c>
@@ -2514,7 +2508,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:21" ht="65.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:21" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
         <v>2234</v>
       </c>
@@ -2579,7 +2573,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="65.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:21" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
         <v>2233</v>
       </c>
@@ -2835,7 +2829,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="65.5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:21" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A27" s="4">
         <v>2219</v>
       </c>
@@ -2900,7 +2894,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="78.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:21" ht="65.5" x14ac:dyDescent="0.35">
       <c r="A28" s="4">
         <v>2215</v>
       </c>
@@ -3416,7 +3410,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="36" spans="1:21" ht="65.5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:21" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A36" s="4">
         <v>2203</v>
       </c>
@@ -3481,7 +3475,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="8">
         <v>2202</v>
       </c>
@@ -3546,47 +3540,89 @@
         <v>66</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10"/>
-      <c r="N38" s="10"/>
-      <c r="O38" s="10"/>
-      <c r="P38" s="10"/>
-      <c r="Q38" s="10"/>
-      <c r="R38" s="10"/>
-      <c r="S38" s="10"/>
-      <c r="T38" s="10"/>
-      <c r="U38" s="10"/>
+    <row r="38" spans="1:21" ht="39.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="4">
+        <v>2201</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H38" s="6">
+        <v>45846.35833333333</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J38" s="6">
+        <v>45847.37777777778</v>
+      </c>
+      <c r="K38" s="5">
+        <v>1217</v>
+      </c>
+      <c r="L38" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="M38" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="N38" s="5">
+        <v>1998</v>
+      </c>
+      <c r="O38" s="5">
+        <v>400000</v>
+      </c>
+      <c r="P38" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q38" s="5">
+        <v>7</v>
+      </c>
+      <c r="R38" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="S38" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="T38" s="5">
+        <v>7</v>
+      </c>
+      <c r="U38" s="5" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="39" spans="1:21" ht="39.5" x14ac:dyDescent="0.35">
       <c r="A39" s="4">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>22</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>141</v>
+        <v>40</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>67</v>
+        <v>173</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>24</v>
@@ -3598,45 +3634,45 @@
         <v>25</v>
       </c>
       <c r="J39" s="6">
-        <v>45847.37777777778</v>
+        <v>45847.517361111109</v>
       </c>
       <c r="K39" s="5">
-        <v>1217</v>
+        <v>2262</v>
       </c>
       <c r="L39" s="5" t="s">
         <v>170</v>
       </c>
       <c r="M39" s="5" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="N39" s="5">
-        <v>1998</v>
+        <v>2013</v>
       </c>
       <c r="O39" s="5">
-        <v>400000</v>
+        <v>215000</v>
       </c>
       <c r="P39" s="5" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q39" s="5">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="R39" s="5" t="s">
         <v>103</v>
       </c>
       <c r="S39" s="5" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
       <c r="T39" s="5">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="U39" s="5" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="39.5" x14ac:dyDescent="0.35">
       <c r="A40" s="4">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>21</v>
@@ -3648,131 +3684,131 @@
         <v>22</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>173</v>
+        <v>49</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>24</v>
       </c>
       <c r="H40" s="6">
-        <v>45846.35833333333</v>
+        <v>45845.767361111109</v>
       </c>
       <c r="I40" s="5" t="s">
         <v>25</v>
       </c>
       <c r="J40" s="6">
-        <v>45847.517361111109</v>
+        <v>45846.445138888892</v>
       </c>
       <c r="K40" s="5">
-        <v>2262</v>
+        <v>2256</v>
       </c>
       <c r="L40" s="5" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="M40" s="5" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="N40" s="5">
-        <v>2013</v>
+        <v>1995</v>
       </c>
       <c r="O40" s="5">
-        <v>215000</v>
+        <v>431000</v>
       </c>
       <c r="P40" s="5" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q40" s="5">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="R40" s="5" t="s">
-        <v>103</v>
+        <v>44</v>
       </c>
       <c r="S40" s="5" t="s">
-        <v>176</v>
+        <v>133</v>
       </c>
       <c r="T40" s="5">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="U40" s="5" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="39.5" x14ac:dyDescent="0.35">
       <c r="A41" s="4">
-        <v>2199</v>
+        <v>2192</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>22</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="G41" s="5" t="s">
         <v>24</v>
       </c>
       <c r="H41" s="6">
-        <v>45845.767361111109</v>
+        <v>45845.638194444444</v>
       </c>
       <c r="I41" s="5" t="s">
         <v>25</v>
       </c>
       <c r="J41" s="6">
-        <v>45846.445138888892</v>
+        <v>45845.750694444447</v>
       </c>
       <c r="K41" s="5">
-        <v>2256</v>
+        <v>581</v>
       </c>
       <c r="L41" s="5" t="s">
-        <v>177</v>
+        <v>100</v>
       </c>
       <c r="M41" s="5" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="N41" s="5">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="O41" s="5">
-        <v>431000</v>
+        <v>370000</v>
       </c>
       <c r="P41" s="5" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q41" s="5">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="R41" s="5" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="S41" s="5" t="s">
-        <v>133</v>
+        <v>72</v>
       </c>
       <c r="T41" s="5">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="U41" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21" ht="39.5" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A42" s="4">
-        <v>2192</v>
+        <v>2189</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>22</v>
@@ -3781,57 +3817,57 @@
         <v>40</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="G42" s="5" t="s">
         <v>24</v>
       </c>
       <c r="H42" s="6">
-        <v>45845.638194444444</v>
+        <v>45845.61041666667</v>
       </c>
       <c r="I42" s="5" t="s">
         <v>25</v>
       </c>
       <c r="J42" s="6">
-        <v>45845.750694444447</v>
+        <v>45851.654861111114</v>
       </c>
       <c r="K42" s="5">
-        <v>581</v>
+        <v>2254</v>
       </c>
       <c r="L42" s="5" t="s">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="M42" s="5" t="s">
-        <v>180</v>
+        <v>35</v>
       </c>
       <c r="N42" s="5">
-        <v>1996</v>
+        <v>2023</v>
       </c>
       <c r="O42" s="5">
-        <v>370000</v>
+        <v>19000</v>
       </c>
       <c r="P42" s="5" t="s">
-        <v>181</v>
+        <v>36</v>
       </c>
       <c r="Q42" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R42" s="5" t="s">
-        <v>103</v>
+        <v>37</v>
       </c>
       <c r="S42" s="5" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
       <c r="T42" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U42" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="43" spans="1:21" ht="52.5" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" ht="39.5" x14ac:dyDescent="0.35">
       <c r="A43" s="4">
-        <v>2189</v>
+        <v>2187</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>21</v>
@@ -3845,58 +3881,58 @@
       <c r="E43" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F43" s="5" t="s">
-        <v>108</v>
+      <c r="F43" s="5">
+        <v>2000</v>
       </c>
       <c r="G43" s="5" t="s">
         <v>24</v>
       </c>
       <c r="H43" s="6">
-        <v>45845.61041666667</v>
+        <v>45845.57916666667</v>
       </c>
       <c r="I43" s="5" t="s">
         <v>25</v>
       </c>
       <c r="J43" s="6">
-        <v>45851.654861111114</v>
+        <v>45846.555555555555</v>
       </c>
       <c r="K43" s="5">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="L43" s="5" t="s">
-        <v>34</v>
+        <v>128</v>
       </c>
       <c r="M43" s="5" t="s">
-        <v>35</v>
+        <v>182</v>
       </c>
       <c r="N43" s="5">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="O43" s="5">
-        <v>19000</v>
+        <v>101531</v>
       </c>
       <c r="P43" s="5" t="s">
-        <v>36</v>
+        <v>183</v>
       </c>
       <c r="Q43" s="5">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="R43" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="S43" s="5" t="s">
-        <v>111</v>
+        <v>184</v>
       </c>
       <c r="T43" s="5">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="U43" s="5" t="s">
-        <v>78</v>
+        <v>140</v>
       </c>
     </row>
     <row r="44" spans="1:21" ht="39.5" x14ac:dyDescent="0.35">
       <c r="A44" s="4">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>21</v>
@@ -3910,186 +3946,184 @@
       <c r="E44" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F44" s="5">
-        <v>2000</v>
+      <c r="F44" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="G44" s="5" t="s">
         <v>24</v>
       </c>
       <c r="H44" s="6">
-        <v>45845.57916666667</v>
+        <v>45845.570833333331</v>
       </c>
       <c r="I44" s="5" t="s">
         <v>25</v>
       </c>
       <c r="J44" s="6">
-        <v>45846.555555555555</v>
+        <v>45845.637499999997</v>
       </c>
       <c r="K44" s="5">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="L44" s="5" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="M44" s="5" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="N44" s="5">
+        <v>2001</v>
+      </c>
+      <c r="O44" s="5">
+        <v>314967</v>
+      </c>
+      <c r="P44" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q44" s="5">
+        <v>3</v>
+      </c>
+      <c r="R44" s="7"/>
+      <c r="S44" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="T44" s="5">
+        <v>3</v>
+      </c>
+      <c r="U44" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" ht="65.5" x14ac:dyDescent="0.35">
+      <c r="A45" s="4">
+        <v>2185</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H45" s="6">
+        <v>45845.546527777777</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J45" s="6">
+        <v>45851.466666666667</v>
+      </c>
+      <c r="K45" s="5">
+        <v>2251</v>
+      </c>
+      <c r="L45" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="M45" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="N45" s="5">
         <v>2017</v>
       </c>
-      <c r="O44" s="5">
-        <v>101531</v>
-      </c>
-      <c r="P44" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q44" s="5">
-        <v>24</v>
-      </c>
-      <c r="R44" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="S44" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="T44" s="5">
-        <v>24</v>
-      </c>
-      <c r="U44" s="5" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="45" spans="1:21" ht="39.5" x14ac:dyDescent="0.35">
-      <c r="A45" s="4">
-        <v>2186</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E45" s="5" t="s">
+      <c r="O45" s="5">
+        <v>155000</v>
+      </c>
+      <c r="P45" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q45" s="5">
+        <v>36</v>
+      </c>
+      <c r="R45" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="S45" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="T45" s="5">
+        <v>6</v>
+      </c>
+      <c r="U45" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" ht="39.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="4">
+        <v>2184</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E46" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F45" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H45" s="6">
-        <v>45845.570833333331</v>
-      </c>
-      <c r="I45" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J45" s="6">
-        <v>45845.637499999997</v>
-      </c>
-      <c r="K45" s="5">
-        <v>2252</v>
-      </c>
-      <c r="L45" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="M45" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="N45" s="5">
-        <v>2001</v>
-      </c>
-      <c r="O45" s="5">
-        <v>314967</v>
-      </c>
-      <c r="P45" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q45" s="5">
-        <v>3</v>
-      </c>
-      <c r="R45" s="7"/>
-      <c r="S45" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="T45" s="5">
-        <v>3</v>
-      </c>
-      <c r="U45" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="46" spans="1:21" ht="65.5" x14ac:dyDescent="0.35">
-      <c r="A46" s="4">
-        <v>2185</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>187</v>
+      <c r="F46" s="5">
+        <v>500</v>
       </c>
       <c r="G46" s="5" t="s">
         <v>24</v>
       </c>
       <c r="H46" s="6">
-        <v>45845.546527777777</v>
+        <v>45845.486111111109</v>
       </c>
       <c r="I46" s="5" t="s">
         <v>25</v>
       </c>
       <c r="J46" s="6">
-        <v>45851.466666666667</v>
+        <v>45845.636805555558</v>
       </c>
       <c r="K46" s="5">
-        <v>2251</v>
+        <v>1543</v>
       </c>
       <c r="L46" s="5" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="M46" s="5" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="N46" s="5">
-        <v>2017</v>
+        <v>2011</v>
       </c>
       <c r="O46" s="5">
-        <v>155000</v>
+        <v>2011</v>
       </c>
       <c r="P46" s="5" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="Q46" s="5">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="R46" s="5" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="S46" s="5" t="s">
-        <v>189</v>
+        <v>104</v>
       </c>
       <c r="T46" s="5">
-        <v>6</v>
-      </c>
-      <c r="U46" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="47" spans="1:21" ht="39.5" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="U46" s="7"/>
+    </row>
+    <row r="47" spans="1:21" ht="65.5" x14ac:dyDescent="0.35">
       <c r="A47" s="4">
-        <v>2184</v>
+        <v>2179</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>21</v>
@@ -4103,62 +4137,64 @@
       <c r="E47" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F47" s="5">
-        <v>500</v>
+      <c r="F47" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>24</v>
       </c>
       <c r="H47" s="6">
-        <v>45845.486111111109</v>
+        <v>45845.40902777778</v>
       </c>
       <c r="I47" s="5" t="s">
         <v>25</v>
       </c>
       <c r="J47" s="6">
-        <v>45845.636805555558</v>
+        <v>45851.460416666669</v>
       </c>
       <c r="K47" s="5">
-        <v>1543</v>
+        <v>1990</v>
       </c>
       <c r="L47" s="5" t="s">
-        <v>142</v>
+        <v>62</v>
       </c>
       <c r="M47" s="5" t="s">
-        <v>190</v>
+        <v>109</v>
       </c>
       <c r="N47" s="5">
-        <v>2011</v>
+        <v>2002</v>
       </c>
       <c r="O47" s="5">
-        <v>2011</v>
+        <v>350000</v>
       </c>
       <c r="P47" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q47" s="5">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="R47" s="5" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="S47" s="5" t="s">
-        <v>104</v>
+        <v>193</v>
       </c>
       <c r="T47" s="5">
-        <v>24</v>
-      </c>
-      <c r="U47" s="7"/>
+        <v>36</v>
+      </c>
+      <c r="U47" s="5" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="48" spans="1:21" ht="65.5" x14ac:dyDescent="0.35">
       <c r="A48" s="4">
-        <v>2179</v>
+        <v>2178</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>22</v>
@@ -4167,63 +4203,63 @@
         <v>40</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>49</v>
+        <v>105</v>
       </c>
       <c r="G48" s="5" t="s">
         <v>24</v>
       </c>
       <c r="H48" s="6">
-        <v>45845.40902777778</v>
+        <v>45845.364583333336</v>
       </c>
       <c r="I48" s="5" t="s">
         <v>25</v>
       </c>
       <c r="J48" s="6">
-        <v>45851.460416666669</v>
+        <v>45845.640972222223</v>
       </c>
       <c r="K48" s="5">
-        <v>1990</v>
+        <v>2223</v>
       </c>
       <c r="L48" s="5" t="s">
-        <v>62</v>
+        <v>170</v>
       </c>
       <c r="M48" s="5" t="s">
-        <v>109</v>
+        <v>194</v>
       </c>
       <c r="N48" s="5">
-        <v>2002</v>
+        <v>2006</v>
       </c>
       <c r="O48" s="5">
-        <v>350000</v>
+        <v>297563</v>
       </c>
       <c r="P48" s="5" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="Q48" s="5">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="R48" s="5" t="s">
-        <v>88</v>
+        <v>196</v>
       </c>
       <c r="S48" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="T48" s="5">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="U48" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="49" spans="1:21" ht="65.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:21" ht="39.5" x14ac:dyDescent="0.35">
       <c r="A49" s="4">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>22</v>
@@ -4231,8 +4267,8 @@
       <c r="E49" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F49" s="5" t="s">
-        <v>105</v>
+      <c r="F49" s="5">
+        <v>400</v>
       </c>
       <c r="G49" s="5" t="s">
         <v>24</v>
@@ -4244,51 +4280,51 @@
         <v>25</v>
       </c>
       <c r="J49" s="6">
-        <v>45845.640972222223</v>
+        <v>45845.445138888892</v>
       </c>
       <c r="K49" s="5">
-        <v>2223</v>
+        <v>1028</v>
       </c>
       <c r="L49" s="5" t="s">
-        <v>170</v>
+        <v>142</v>
       </c>
       <c r="M49" s="5" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N49" s="5">
-        <v>2006</v>
+        <v>1998</v>
       </c>
       <c r="O49" s="5">
-        <v>297563</v>
+        <v>300000</v>
       </c>
       <c r="P49" s="5" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Q49" s="5">
         <v>24</v>
       </c>
       <c r="R49" s="5" t="s">
-        <v>196</v>
+        <v>44</v>
       </c>
       <c r="S49" s="5" t="s">
-        <v>197</v>
+        <v>45</v>
       </c>
       <c r="T49" s="5">
         <v>24</v>
       </c>
       <c r="U49" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="50" spans="1:21" ht="39.5" x14ac:dyDescent="0.35">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A50" s="4">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>22</v>
@@ -4297,7 +4333,7 @@
         <v>40</v>
       </c>
       <c r="F50" s="5">
-        <v>400</v>
+        <v>1800</v>
       </c>
       <c r="G50" s="5" t="s">
         <v>24</v>
@@ -4309,45 +4345,45 @@
         <v>25</v>
       </c>
       <c r="J50" s="6">
-        <v>45845.445138888892</v>
+        <v>45845.45208333333</v>
       </c>
       <c r="K50" s="5">
-        <v>1028</v>
+        <v>2239</v>
       </c>
       <c r="L50" s="5" t="s">
-        <v>142</v>
+        <v>92</v>
       </c>
       <c r="M50" s="5" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="N50" s="5">
-        <v>1998</v>
+        <v>2001</v>
       </c>
       <c r="O50" s="5">
-        <v>300000</v>
+        <v>630000</v>
       </c>
       <c r="P50" s="5" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q50" s="5">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="R50" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="S50" s="5" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="T50" s="5">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="U50" s="5" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51" spans="1:21" ht="52.5" x14ac:dyDescent="0.35">
       <c r="A51" s="4">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>21</v>
@@ -4359,144 +4395,56 @@
         <v>22</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F51" s="5">
-        <v>1800</v>
+        <v>141</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>202</v>
       </c>
       <c r="G51" s="5" t="s">
         <v>24</v>
       </c>
       <c r="H51" s="6">
-        <v>45845.364583333336</v>
+        <v>45845.363888888889</v>
       </c>
       <c r="I51" s="5" t="s">
         <v>25</v>
       </c>
       <c r="J51" s="6">
-        <v>45845.45208333333</v>
+        <v>45845.368055555555</v>
       </c>
       <c r="K51" s="5">
-        <v>2239</v>
+        <v>2209</v>
       </c>
       <c r="L51" s="5" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="M51" s="5" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="N51" s="5">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="O51" s="5">
-        <v>630000</v>
+        <v>274000</v>
       </c>
       <c r="P51" s="5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="Q51" s="5">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="R51" s="5" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="S51" s="5" t="s">
-        <v>29</v>
+        <v>205</v>
       </c>
       <c r="T51" s="5">
-        <v>12</v>
-      </c>
-      <c r="U51" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="52" spans="1:21" ht="52.5" x14ac:dyDescent="0.35">
-      <c r="A52" s="4">
-        <v>2175</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="F52" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="G52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H52" s="6">
-        <v>45845.363888888889</v>
-      </c>
-      <c r="I52" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="J52" s="6">
-        <v>45845.368055555555</v>
-      </c>
-      <c r="K52" s="5">
-        <v>2209</v>
-      </c>
-      <c r="L52" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="M52" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="N52" s="5">
-        <v>2002</v>
-      </c>
-      <c r="O52" s="5">
-        <v>274000</v>
-      </c>
-      <c r="P52" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q52" s="5">
         <v>1</v>
       </c>
-      <c r="R52" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="S52" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="T52" s="5">
-        <v>1</v>
-      </c>
-      <c r="U52" s="7"/>
+      <c r="U51" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="S37:S38"/>
-    <mergeCell ref="T37:T38"/>
-    <mergeCell ref="U37:U38"/>
-    <mergeCell ref="M37:M38"/>
-    <mergeCell ref="N37:N38"/>
-    <mergeCell ref="O37:O38"/>
-    <mergeCell ref="P37:P38"/>
-    <mergeCell ref="Q37:Q38"/>
-    <mergeCell ref="R37:R38"/>
-    <mergeCell ref="G37:G38"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="I37:I38"/>
-    <mergeCell ref="J37:J38"/>
-    <mergeCell ref="K37:K38"/>
-    <mergeCell ref="L37:L38"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="C37:C38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="E37:E38"/>
-    <mergeCell ref="F37:F38"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>